--- a/Raw/field_UWS.xlsx
+++ b/Raw/field_UWS.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mnhnfr.sharepoint.com/sites/ParisWildness/Documents partages/General/Data/UWS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42DB75CA-EE91-4750-BF12-5B2C72FEE7C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{087AADCE-169F-4340-A908-037967EBD577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A2E2B354-4CFC-4A8A-96B7-F1F306D34BE6}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_field" sheetId="5" r:id="rId1"/>
+    <sheet name="Feuil1" sheetId="6" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Data_field!$A$4:$A$27</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Data_field!$AG$4:$AG$27</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">Data_field!$A$4:$A$26</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Data_field!$AG$4:$AG$26</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -692,97 +693,97 @@
     <t>sans liane</t>
   </si>
   <si>
+    <t>48.88012, 2.3985</t>
+  </si>
+  <si>
+    <t>48.88451, 2.39577</t>
+  </si>
+  <si>
+    <t>48.88599, 2.3981</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>48.88568, 2.38995</t>
+  </si>
+  <si>
+    <t>Even</t>
+  </si>
+  <si>
+    <t>48.89055, 2.38671</t>
+  </si>
+  <si>
+    <t>48.89808, 2.38228</t>
+  </si>
+  <si>
+    <t>Tram</t>
+  </si>
+  <si>
+    <t>abandonné pour sdmr</t>
+  </si>
+  <si>
+    <t>48.87804, 2.40557</t>
+  </si>
+  <si>
+    <t>48.89002, 2.39686</t>
+  </si>
+  <si>
+    <t>Stade</t>
+  </si>
+  <si>
+    <t>48.87811, 2.38777</t>
+  </si>
+  <si>
+    <t>48.87679, 2.38535</t>
+  </si>
+  <si>
+    <t>48.87498, 2.38588</t>
+  </si>
+  <si>
+    <t>7e</t>
+  </si>
+  <si>
+    <t>48.8489, 2.30459</t>
+  </si>
+  <si>
+    <t>48.85007, 2.31233</t>
+  </si>
+  <si>
+    <t>Pelouse</t>
+  </si>
+  <si>
+    <t>48.85041, 2.31423</t>
+  </si>
+  <si>
+    <t>Square</t>
+  </si>
+  <si>
+    <t>48.85052, 2.31954</t>
+  </si>
+  <si>
+    <t>48.85575, 2.31666</t>
+  </si>
+  <si>
+    <t>48.858, 2.3199</t>
+  </si>
+  <si>
+    <t>48.85878, 2.30344</t>
+  </si>
+  <si>
+    <t>48.86041, 2.30275</t>
+  </si>
+  <si>
+    <t>48.85626, 2.29503</t>
+  </si>
+  <si>
+    <t>48.85511, 2.296</t>
+  </si>
+  <si>
+    <t>Parc</t>
+  </si>
+  <si>
     <t>avec liane</t>
-  </si>
-  <si>
-    <t>48.88012, 2.3985</t>
-  </si>
-  <si>
-    <t>48.88451, 2.39577</t>
-  </si>
-  <si>
-    <t>48.88599, 2.3981</t>
-  </si>
-  <si>
-    <t>/</t>
-  </si>
-  <si>
-    <t>48.88568, 2.38995</t>
-  </si>
-  <si>
-    <t>Even</t>
-  </si>
-  <si>
-    <t>48.89055, 2.38671</t>
-  </si>
-  <si>
-    <t>48.89808, 2.38228</t>
-  </si>
-  <si>
-    <t>Tram</t>
-  </si>
-  <si>
-    <t>abandonné pour sdmr</t>
-  </si>
-  <si>
-    <t>48.87804, 2.40557</t>
-  </si>
-  <si>
-    <t>48.89002, 2.39686</t>
-  </si>
-  <si>
-    <t>Stade</t>
-  </si>
-  <si>
-    <t>48.87811, 2.38777</t>
-  </si>
-  <si>
-    <t>48.87679, 2.38535</t>
-  </si>
-  <si>
-    <t>48.87498, 2.38588</t>
-  </si>
-  <si>
-    <t>7e</t>
-  </si>
-  <si>
-    <t>48.8489, 2.30459</t>
-  </si>
-  <si>
-    <t>48.85007, 2.31233</t>
-  </si>
-  <si>
-    <t>Pelouse</t>
-  </si>
-  <si>
-    <t>48.85041, 2.31423</t>
-  </si>
-  <si>
-    <t>Square</t>
-  </si>
-  <si>
-    <t>48.85052, 2.31954</t>
-  </si>
-  <si>
-    <t>48.85575, 2.31666</t>
-  </si>
-  <si>
-    <t>48.858, 2.3199</t>
-  </si>
-  <si>
-    <t>48.85878, 2.30344</t>
-  </si>
-  <si>
-    <t>48.86041, 2.30275</t>
-  </si>
-  <si>
-    <t>48.85626, 2.29503</t>
-  </si>
-  <si>
-    <t>48.85511, 2.296</t>
-  </si>
-  <si>
-    <t>Parc</t>
   </si>
 </sst>
 </file>
@@ -1787,16 +1788,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>43</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
@@ -1832,8 +1833,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="48015525" y="1047750"/>
-              <a:ext cx="3286125" cy="3419475"/>
+              <a:off x="45262800" y="1009650"/>
+              <a:ext cx="3286125" cy="3228975"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2183,7 +2184,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD31EF42-CD6F-4144-8202-D50E1E1A911D}">
-  <dimension ref="A1:AI59"/>
+  <dimension ref="A1:AI58"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.7109375" style="1" customWidth="1"/>
@@ -2412,19 +2413,19 @@
         <v>0</v>
       </c>
       <c r="Z3" s="1">
-        <f t="shared" ref="Z3:Z5" si="0">SUM(J3:O3)</f>
+        <f>SUM(J3:O3)</f>
         <v>6</v>
       </c>
       <c r="AA3" s="1">
-        <f t="shared" ref="AA3:AA7" si="1">SUM(P3:T3)</f>
+        <f>SUM(P3:T3)</f>
         <v>2</v>
       </c>
       <c r="AB3" s="1">
-        <f t="shared" ref="AB3:AB7" si="2">SUM(U3:Y3)</f>
+        <f>SUM(U3:Y3)</f>
         <v>1</v>
       </c>
       <c r="AC3" s="1">
-        <f t="shared" ref="AC3:AC7" si="3">SUM(Z3:AB3)</f>
+        <f>SUM(Z3:AB3)</f>
         <v>9</v>
       </c>
       <c r="AD3" s="1">
@@ -2432,7 +2433,7 @@
         <v>5</v>
       </c>
       <c r="AE3" s="1">
-        <f t="shared" ref="AE3:AE27" si="4">AA3/5*5</f>
+        <f>AA3/5*5</f>
         <v>2</v>
       </c>
       <c r="AF3" s="1">
@@ -2521,35 +2522,35 @@
         <v>0</v>
       </c>
       <c r="Z4" s="1">
-        <f t="shared" si="0"/>
+        <f>SUM(J4:O4)</f>
         <v>4</v>
       </c>
       <c r="AA4" s="1">
-        <f t="shared" si="1"/>
+        <f>SUM(P4:T4)</f>
         <v>1</v>
       </c>
       <c r="AB4" s="1">
-        <f t="shared" si="2"/>
+        <f>SUM(U4:Y4)</f>
         <v>3</v>
       </c>
       <c r="AC4" s="1">
-        <f t="shared" si="3"/>
+        <f>SUM(Z4:AB4)</f>
         <v>8</v>
       </c>
       <c r="AD4" s="1">
-        <f t="shared" ref="AD4:AD27" si="5">Z4/6*5</f>
+        <f>Z4/6*5</f>
         <v>3.333333333333333</v>
       </c>
       <c r="AE4" s="1">
-        <f t="shared" si="4"/>
+        <f>AA4/5*5</f>
         <v>1</v>
       </c>
       <c r="AF4" s="1">
-        <f t="shared" ref="AF4:AF27" si="6" xml:space="preserve"> AB4/5*5</f>
+        <f xml:space="preserve"> AB4/5*5</f>
         <v>3</v>
       </c>
       <c r="AG4" s="1">
-        <f t="shared" ref="AG4:AG27" si="7">SUM(AD4:AF4)/3</f>
+        <f>SUM(AD4:AF4)/3</f>
         <v>2.4444444444444442</v>
       </c>
       <c r="AI4" s="23"/>
@@ -2631,35 +2632,35 @@
         <v>0</v>
       </c>
       <c r="Z5" s="1">
-        <f t="shared" si="0"/>
+        <f>SUM(J5:O5)</f>
         <v>1</v>
       </c>
       <c r="AA5" s="1">
-        <f t="shared" si="1"/>
+        <f>SUM(P5:T5)</f>
         <v>2</v>
       </c>
       <c r="AB5" s="1">
-        <f t="shared" si="2"/>
+        <f>SUM(U5:Y5)</f>
         <v>2</v>
       </c>
       <c r="AC5" s="1">
-        <f t="shared" si="3"/>
+        <f>SUM(Z5:AB5)</f>
         <v>5</v>
       </c>
       <c r="AD5" s="1">
-        <f t="shared" si="5"/>
+        <f>Z5/6*5</f>
         <v>0.83333333333333326</v>
       </c>
       <c r="AE5" s="1">
-        <f t="shared" si="4"/>
+        <f>AA5/5*5</f>
         <v>2</v>
       </c>
       <c r="AF5" s="1">
-        <f t="shared" si="6"/>
+        <f xml:space="preserve"> AB5/5*5</f>
         <v>2</v>
       </c>
       <c r="AG5" s="1">
-        <f t="shared" si="7"/>
+        <f>SUM(AD5:AF5)/3</f>
         <v>1.6111111111111109</v>
       </c>
       <c r="AH5" s="1" t="s">
@@ -2671,19 +2672,19 @@
         <v>42</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C6" s="15">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D6" s="15">
         <v>1</v>
       </c>
       <c r="E6" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>41</v>
@@ -2692,19 +2693,19 @@
         <v>46126</v>
       </c>
       <c r="I6" s="1">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J6" s="1">
         <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" s="1">
         <v>1</v>
       </c>
       <c r="M6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" s="1">
         <v>1</v>
@@ -2716,9 +2717,9 @@
         <v>0</v>
       </c>
       <c r="Q6" s="1">
-        <v>1</v>
-      </c>
-      <c r="R6" s="22">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1">
         <v>1</v>
       </c>
       <c r="S6" s="1">
@@ -2728,7 +2729,7 @@
         <v>0</v>
       </c>
       <c r="U6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="1">
         <v>1</v>
@@ -2736,48 +2737,44 @@
       <c r="W6" s="1">
         <v>0</v>
       </c>
-      <c r="X6" s="22">
-        <v>0</v>
+      <c r="X6" s="1">
+        <v>1</v>
       </c>
       <c r="Y6" s="22">
         <v>0</v>
       </c>
       <c r="Z6" s="1">
-        <f t="shared" ref="Z6:Z7" si="8">SUM(J6:O6)</f>
+        <f>SUM(J6:O6)</f>
         <v>4</v>
       </c>
       <c r="AA6" s="1">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f>SUM(P6:T6)</f>
+        <v>1</v>
       </c>
       <c r="AB6" s="1">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>SUM(U6:Y6)</f>
+        <v>3</v>
       </c>
       <c r="AC6" s="1">
-        <f t="shared" si="3"/>
-        <v>7</v>
+        <f>SUM(Z6:AB6)</f>
+        <v>8</v>
       </c>
       <c r="AD6" s="1">
-        <f t="shared" si="5"/>
+        <f>Z6/6*5</f>
         <v>3.333333333333333</v>
       </c>
       <c r="AE6" s="1">
-        <f t="shared" si="4"/>
-        <v>2</v>
+        <f>AA6/5*5</f>
+        <v>1</v>
       </c>
       <c r="AF6" s="1">
-        <f t="shared" si="6"/>
-        <v>1</v>
+        <f xml:space="preserve"> AB6/5*5</f>
+        <v>3</v>
       </c>
       <c r="AG6" s="1">
-        <f t="shared" si="7"/>
-        <v>2.1111111111111112</v>
-      </c>
-      <c r="AH6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI6" s="23"/>
+        <f>SUM(AD6:AF6)/3</f>
+        <v>2.4444444444444442</v>
+      </c>
     </row>
     <row r="7" spans="1:35">
       <c r="A7" s="1" t="s">
@@ -2787,7 +2784,7 @@
         <v>47</v>
       </c>
       <c r="C7" s="15">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D7" s="15">
         <v>1</v>
@@ -2805,88 +2802,89 @@
         <v>46126</v>
       </c>
       <c r="I7" s="1">
+        <v>2</v>
+      </c>
+      <c r="J7" s="1">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>1</v>
+      </c>
+      <c r="N7" s="22">
+        <v>1</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="22">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1">
+        <v>1</v>
+      </c>
+      <c r="S7" s="1">
+        <v>0</v>
+      </c>
+      <c r="T7" s="1">
+        <v>0</v>
+      </c>
+      <c r="U7" s="1">
+        <v>1</v>
+      </c>
+      <c r="V7" s="1">
+        <v>1</v>
+      </c>
+      <c r="W7" s="22">
+        <v>0</v>
+      </c>
+      <c r="X7" s="22">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="22">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="1">
+        <f t="shared" ref="Z7:Z11" si="0">SUM(J7:O7)</f>
+        <v>3</v>
+      </c>
+      <c r="AA7" s="1">
+        <f t="shared" ref="AA7:AA11" si="1">SUM(P7:T7)</f>
+        <v>2</v>
+      </c>
+      <c r="AB7" s="1">
+        <f t="shared" ref="AB7:AB11" si="2">SUM(U7:Y7)</f>
+        <v>3</v>
+      </c>
+      <c r="AC7" s="1">
+        <f t="shared" ref="AC7:AC11" si="3">SUM(Z7:AB7)</f>
+        <v>8</v>
+      </c>
+      <c r="AD7" s="1">
+        <f>Z7/6*5</f>
         <v>2.5</v>
       </c>
-      <c r="J7" s="1">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-      <c r="L7" s="1">
-        <v>1</v>
-      </c>
-      <c r="M7" s="1">
-        <v>1</v>
-      </c>
-      <c r="N7" s="1">
-        <v>1</v>
-      </c>
-      <c r="O7" s="1">
-        <v>0</v>
-      </c>
-      <c r="P7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
-      <c r="R7" s="1">
-        <v>1</v>
-      </c>
-      <c r="S7" s="1">
-        <v>0</v>
-      </c>
-      <c r="T7" s="1">
-        <v>0</v>
-      </c>
-      <c r="U7" s="1">
-        <v>1</v>
-      </c>
-      <c r="V7" s="1">
-        <v>1</v>
-      </c>
-      <c r="W7" s="1">
-        <v>0</v>
-      </c>
-      <c r="X7" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="22">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="1">
-        <f t="shared" si="8"/>
-        <v>4</v>
-      </c>
-      <c r="AA7" s="1">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AB7" s="1">
-        <f t="shared" si="2"/>
+      <c r="AE7" s="1">
+        <f>AA7/5*5</f>
+        <v>2</v>
+      </c>
+      <c r="AF7" s="1">
+        <f xml:space="preserve"> AB7/5*5</f>
         <v>3</v>
       </c>
-      <c r="AC7" s="1">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-      <c r="AD7" s="1">
-        <f t="shared" si="5"/>
-        <v>3.333333333333333</v>
-      </c>
-      <c r="AE7" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AF7" s="1">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
       <c r="AG7" s="1">
-        <f t="shared" si="7"/>
-        <v>2.4444444444444442</v>
-      </c>
+        <f>SUM(AD7:AF7)/3</f>
+        <v>2.5</v>
+      </c>
+      <c r="AI7" s="24"/>
     </row>
     <row r="8" spans="1:35">
       <c r="A8" s="1" t="s">
@@ -2896,7 +2894,7 @@
         <v>48</v>
       </c>
       <c r="C8" s="15">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D8" s="15">
         <v>1</v>
@@ -2908,37 +2906,37 @@
         <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="H8" s="27">
         <v>46126</v>
       </c>
       <c r="I8" s="1">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J8" s="1">
         <v>1</v>
       </c>
       <c r="K8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" s="22">
         <v>1</v>
       </c>
       <c r="O8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="22">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>1</v>
       </c>
       <c r="R8" s="1">
         <v>1</v>
@@ -2965,48 +2963,48 @@
         <v>0</v>
       </c>
       <c r="Z8" s="1">
-        <f t="shared" ref="Z8:Z12" si="9">SUM(J8:O8)</f>
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="AA8" s="1">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AB8" s="1">
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="AA8" s="1">
-        <f t="shared" ref="AA8:AA12" si="10">SUM(P8:T8)</f>
-        <v>2</v>
-      </c>
-      <c r="AB8" s="1">
-        <f t="shared" ref="AB8:AB12" si="11">SUM(U8:Y8)</f>
+      <c r="AC8" s="1">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="AD8" s="1">
+        <f>Z8/6*5</f>
+        <v>4.166666666666667</v>
+      </c>
+      <c r="AE8" s="1">
+        <f>AA8/5*5</f>
+        <v>2</v>
+      </c>
+      <c r="AF8" s="1">
+        <f xml:space="preserve"> AB8/5*5</f>
         <v>3</v>
       </c>
-      <c r="AC8" s="1">
-        <f t="shared" ref="AC8:AC12" si="12">SUM(Z8:AB8)</f>
-        <v>8</v>
-      </c>
-      <c r="AD8" s="1">
-        <f t="shared" si="5"/>
-        <v>2.5</v>
-      </c>
-      <c r="AE8" s="1">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="AF8" s="1">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
       <c r="AG8" s="1">
-        <f t="shared" si="7"/>
-        <v>2.5</v>
-      </c>
-      <c r="AI8" s="24"/>
+        <f>SUM(AD8:AF8)/3</f>
+        <v>3.0555555555555558</v>
+      </c>
+      <c r="AI8" s="23"/>
     </row>
     <row r="9" spans="1:35">
       <c r="A9" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C9" s="15">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D9" s="15">
         <v>1</v>
@@ -3018,7 +3016,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H9" s="27">
         <v>46126</v>
@@ -3036,16 +3034,16 @@
         <v>1</v>
       </c>
       <c r="M9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="22">
         <v>1</v>
       </c>
       <c r="O9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="1">
         <v>1</v>
@@ -3075,48 +3073,48 @@
         <v>0</v>
       </c>
       <c r="Z9" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="AA9" s="1">
-        <f t="shared" si="10"/>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="AB9" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="AC9" s="1">
-        <f t="shared" si="12"/>
-        <v>10</v>
+        <f t="shared" si="3"/>
+        <v>11</v>
       </c>
       <c r="AD9" s="1">
-        <f t="shared" si="5"/>
+        <f>Z9/6*5</f>
         <v>4.166666666666667</v>
       </c>
       <c r="AE9" s="1">
-        <f t="shared" si="4"/>
-        <v>2</v>
+        <f>AA9/5*5</f>
+        <v>3</v>
       </c>
       <c r="AF9" s="1">
-        <f t="shared" si="6"/>
+        <f xml:space="preserve"> AB9/5*5</f>
         <v>3</v>
       </c>
       <c r="AG9" s="1">
-        <f t="shared" si="7"/>
-        <v>3.0555555555555558</v>
-      </c>
-      <c r="AI9" s="23"/>
+        <f>SUM(AD9:AF9)/3</f>
+        <v>3.3888888888888893</v>
+      </c>
+      <c r="AI9" s="25"/>
     </row>
     <row r="10" spans="1:35">
       <c r="A10" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C10" s="15">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D10" s="15">
         <v>1</v>
@@ -3128,13 +3126,13 @@
         <v>2</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="H10" s="27">
         <v>46126</v>
       </c>
       <c r="I10" s="1">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J10" s="1">
         <v>1</v>
@@ -3146,7 +3144,7 @@
         <v>1</v>
       </c>
       <c r="M10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" s="22">
         <v>1</v>
@@ -3155,7 +3153,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="1">
         <v>1</v>
@@ -3170,7 +3168,7 @@
         <v>0</v>
       </c>
       <c r="U10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="1">
         <v>1</v>
@@ -3182,41 +3180,41 @@
         <v>1</v>
       </c>
       <c r="Y10" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" s="1">
-        <f t="shared" si="9"/>
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="AA10" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AB10" s="1">
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="AB10" s="1">
-        <f t="shared" si="11"/>
+      <c r="AC10" s="1">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="AD10" s="1">
+        <f>Z10/6*5</f>
+        <v>3.333333333333333</v>
+      </c>
+      <c r="AE10" s="1">
+        <f>AA10/5*5</f>
+        <v>2</v>
+      </c>
+      <c r="AF10" s="1">
+        <f xml:space="preserve"> AB10/5*5</f>
         <v>3</v>
       </c>
-      <c r="AC10" s="1">
-        <f t="shared" si="12"/>
-        <v>11</v>
-      </c>
-      <c r="AD10" s="1">
-        <f t="shared" si="5"/>
-        <v>4.166666666666667</v>
-      </c>
-      <c r="AE10" s="1">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="AF10" s="1">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
       <c r="AG10" s="1">
-        <f t="shared" si="7"/>
-        <v>3.3888888888888893</v>
-      </c>
-      <c r="AI10" s="25"/>
+        <f>SUM(AD10:AF10)/3</f>
+        <v>2.7777777777777772</v>
+      </c>
+      <c r="AI10" s="23"/>
     </row>
     <row r="11" spans="1:35">
       <c r="A11" s="1" t="s">
@@ -3226,7 +3224,7 @@
         <v>53</v>
       </c>
       <c r="C11" s="15">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D11" s="15">
         <v>1</v>
@@ -3238,13 +3236,13 @@
         <v>2</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="H11" s="27">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="I11" s="1">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J11" s="1">
         <v>1</v>
@@ -3253,16 +3251,16 @@
         <v>1</v>
       </c>
       <c r="L11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="1">
-        <v>0</v>
-      </c>
-      <c r="N11" s="22">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1">
         <v>1</v>
       </c>
       <c r="O11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" s="1">
         <v>0</v>
@@ -3280,75 +3278,77 @@
         <v>0</v>
       </c>
       <c r="U11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="1">
         <v>1</v>
       </c>
-      <c r="W11" s="22">
-        <v>0</v>
-      </c>
-      <c r="X11" s="22">
+      <c r="W11" s="1">
+        <v>0</v>
+      </c>
+      <c r="X11" s="1">
         <v>1</v>
       </c>
       <c r="Y11" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="1">
-        <f t="shared" si="9"/>
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="AA11" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="AB11" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="AC11" s="1">
-        <f t="shared" si="12"/>
-        <v>9</v>
+        <f t="shared" si="3"/>
+        <v>10</v>
       </c>
       <c r="AD11" s="1">
-        <f t="shared" si="5"/>
-        <v>3.333333333333333</v>
+        <f>Z11/6*5</f>
+        <v>4.166666666666667</v>
       </c>
       <c r="AE11" s="1">
-        <f t="shared" si="4"/>
+        <f>AA11/5*5</f>
         <v>2</v>
       </c>
       <c r="AF11" s="1">
-        <f t="shared" si="6"/>
+        <f xml:space="preserve"> AB11/5*5</f>
         <v>3</v>
       </c>
       <c r="AG11" s="1">
-        <f t="shared" si="7"/>
-        <v>2.7777777777777772</v>
-      </c>
-      <c r="AI11" s="23"/>
+        <f>SUM(AD11:AF11)/3</f>
+        <v>3.0555555555555558</v>
+      </c>
+      <c r="AH11" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="12" spans="1:35">
       <c r="A12" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B12" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="15">
+        <v>32</v>
+      </c>
+      <c r="D12" s="15">
+        <v>1</v>
+      </c>
+      <c r="E12" s="15">
+        <v>0</v>
+      </c>
+      <c r="F12" s="15">
+        <v>2</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="C12" s="15">
-        <v>21</v>
-      </c>
-      <c r="D12" s="15">
-        <v>1</v>
-      </c>
-      <c r="E12" s="15">
-        <v>0</v>
-      </c>
-      <c r="F12" s="15">
-        <v>2</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="H12" s="27">
         <v>46127</v>
@@ -3363,7 +3363,7 @@
         <v>1</v>
       </c>
       <c r="L12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="1">
         <v>1</v>
@@ -3387,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="T12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" s="1">
         <v>1</v>
@@ -3399,45 +3399,42 @@
         <v>0</v>
       </c>
       <c r="X12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="22">
         <v>0</v>
       </c>
       <c r="Z12" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="Z12:Z21" si="4">SUM(J12:O12)</f>
+        <v>6</v>
+      </c>
+      <c r="AA12" s="1">
+        <f t="shared" ref="AA12:AA21" si="5">SUM(P12:T12)</f>
+        <v>3</v>
+      </c>
+      <c r="AB12" s="1">
+        <f t="shared" ref="AB12:AB21" si="6">SUM(U12:Y12)</f>
+        <v>2</v>
+      </c>
+      <c r="AC12" s="1">
+        <f t="shared" ref="AC12:AC21" si="7">SUM(Z12:AB12)</f>
+        <v>11</v>
+      </c>
+      <c r="AD12" s="1">
+        <f t="shared" ref="AD12:AD21" si="8">Z12/6*5</f>
         <v>5</v>
       </c>
-      <c r="AA12" s="1">
-        <f t="shared" si="10"/>
-        <v>2</v>
-      </c>
-      <c r="AB12" s="1">
-        <f t="shared" si="11"/>
+      <c r="AE12" s="1">
+        <f t="shared" ref="AE12:AE21" si="9">AA12/5*5</f>
         <v>3</v>
       </c>
-      <c r="AC12" s="1">
-        <f t="shared" si="12"/>
-        <v>10</v>
-      </c>
-      <c r="AD12" s="1">
-        <f t="shared" si="5"/>
-        <v>4.166666666666667</v>
-      </c>
-      <c r="AE12" s="1">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
       <c r="AF12" s="1">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f t="shared" ref="AF12:AF21" si="10" xml:space="preserve"> AB12/5*5</f>
+        <v>2</v>
       </c>
       <c r="AG12" s="1">
-        <f t="shared" si="7"/>
-        <v>3.0555555555555558</v>
-      </c>
-      <c r="AH12" s="1" t="s">
-        <v>56</v>
+        <f t="shared" ref="AG12:AG21" si="11">SUM(AD12:AF12)/3</f>
+        <v>3.3333333333333335</v>
       </c>
     </row>
     <row r="13" spans="1:35">
@@ -3448,7 +3445,7 @@
         <v>57</v>
       </c>
       <c r="C13" s="15">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D13" s="15">
         <v>1</v>
@@ -3457,96 +3454,96 @@
         <v>0</v>
       </c>
       <c r="F13" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H13" s="27">
         <v>46127</v>
       </c>
       <c r="I13" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1">
+        <v>0</v>
+      </c>
+      <c r="P13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>1</v>
+      </c>
+      <c r="R13" s="1">
+        <v>0</v>
+      </c>
+      <c r="S13" s="1">
+        <v>0</v>
+      </c>
+      <c r="T13" s="1">
+        <v>0</v>
+      </c>
+      <c r="U13" s="1">
+        <v>0</v>
+      </c>
+      <c r="V13" s="1">
+        <v>1</v>
+      </c>
+      <c r="W13" s="1">
+        <v>0</v>
+      </c>
+      <c r="X13" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="1">
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="J13" s="1">
-        <v>1</v>
-      </c>
-      <c r="K13" s="1">
-        <v>1</v>
-      </c>
-      <c r="L13" s="1">
-        <v>1</v>
-      </c>
-      <c r="M13" s="1">
-        <v>1</v>
-      </c>
-      <c r="N13" s="1">
-        <v>1</v>
-      </c>
-      <c r="O13" s="1">
-        <v>1</v>
-      </c>
-      <c r="P13" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>1</v>
-      </c>
-      <c r="R13" s="1">
-        <v>1</v>
-      </c>
-      <c r="S13" s="1">
-        <v>0</v>
-      </c>
-      <c r="T13" s="1">
-        <v>1</v>
-      </c>
-      <c r="U13" s="1">
-        <v>1</v>
-      </c>
-      <c r="V13" s="1">
-        <v>1</v>
-      </c>
-      <c r="W13" s="1">
-        <v>0</v>
-      </c>
-      <c r="X13" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="22">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="1">
-        <f t="shared" ref="Z13:Z22" si="13">SUM(J13:O13)</f>
-        <v>6</v>
-      </c>
       <c r="AA13" s="1">
-        <f t="shared" ref="AA13:AA22" si="14">SUM(P13:T13)</f>
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="AB13" s="1">
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="AB13" s="1">
-        <f t="shared" ref="AB13:AB22" si="15">SUM(U13:Y13)</f>
-        <v>2</v>
-      </c>
       <c r="AC13" s="1">
-        <f t="shared" ref="AC13:AC22" si="16">SUM(Z13:AB13)</f>
-        <v>11</v>
+        <f t="shared" si="7"/>
+        <v>7</v>
       </c>
       <c r="AD13" s="1">
-        <f t="shared" ref="AD13:AD22" si="17">Z13/6*5</f>
-        <v>5</v>
+        <f t="shared" si="8"/>
+        <v>2.5</v>
       </c>
       <c r="AE13" s="1">
-        <f t="shared" ref="AE13:AE22" si="18">AA13/5*5</f>
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AF13" s="1">
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
-      <c r="AF13" s="1">
-        <f t="shared" ref="AF13:AF22" si="19" xml:space="preserve"> AB13/5*5</f>
-        <v>2</v>
-      </c>
       <c r="AG13" s="1">
-        <f t="shared" ref="AG13:AG22" si="20">SUM(AD13:AF13)/3</f>
-        <v>3.3333333333333335</v>
+        <f t="shared" si="11"/>
+        <v>2.1666666666666665</v>
       </c>
     </row>
     <row r="14" spans="1:35">
@@ -3554,43 +3551,43 @@
         <v>42</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C14" s="15">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="D14" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="15">
         <v>0</v>
       </c>
       <c r="F14" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="H14" s="27">
         <v>46127</v>
       </c>
       <c r="I14" s="1">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J14" s="1">
         <v>1</v>
       </c>
       <c r="K14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="1">
         <v>0</v>
       </c>
       <c r="M14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" s="1">
         <v>0</v>
@@ -3599,7 +3596,7 @@
         <v>0</v>
       </c>
       <c r="Q14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" s="1">
         <v>0</v>
@@ -3614,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W14" s="1">
         <v>0</v>
@@ -3626,36 +3623,36 @@
         <v>1</v>
       </c>
       <c r="Z14" s="1">
-        <f t="shared" si="13"/>
-        <v>3</v>
+        <f t="shared" si="4"/>
+        <v>2</v>
       </c>
       <c r="AA14" s="1">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="AB14" s="1">
-        <f t="shared" si="15"/>
-        <v>3</v>
+        <f t="shared" si="6"/>
+        <v>2</v>
       </c>
       <c r="AC14" s="1">
-        <f t="shared" si="16"/>
-        <v>7</v>
+        <f t="shared" si="7"/>
+        <v>4</v>
       </c>
       <c r="AD14" s="1">
-        <f t="shared" si="17"/>
-        <v>2.5</v>
+        <f t="shared" si="8"/>
+        <v>1.6666666666666665</v>
       </c>
       <c r="AE14" s="1">
-        <f t="shared" si="18"/>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="AF14" s="1">
-        <f t="shared" si="19"/>
-        <v>3</v>
+        <f t="shared" si="10"/>
+        <v>2</v>
       </c>
       <c r="AG14" s="1">
-        <f t="shared" si="20"/>
-        <v>2.1666666666666665</v>
+        <f t="shared" si="11"/>
+        <v>1.2222222222222221</v>
       </c>
     </row>
     <row r="15" spans="1:35">
@@ -3666,10 +3663,10 @@
         <v>60</v>
       </c>
       <c r="C15" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D15" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
         <v>0</v>
@@ -3678,93 +3675,93 @@
         <v>2</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="H15" s="27">
         <v>46127</v>
       </c>
       <c r="I15" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J15" s="1">
         <v>1</v>
       </c>
       <c r="K15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="1">
         <v>1</v>
       </c>
       <c r="O15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" s="1">
         <v>0</v>
       </c>
       <c r="Q15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" s="1">
         <v>0</v>
       </c>
       <c r="T15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W15" s="1">
         <v>0</v>
       </c>
       <c r="X15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="1">
-        <f t="shared" si="13"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>6</v>
       </c>
       <c r="AA15" s="1">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>3</v>
       </c>
       <c r="AB15" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="AC15" s="1">
-        <f t="shared" si="16"/>
-        <v>4</v>
+        <f t="shared" si="7"/>
+        <v>11</v>
       </c>
       <c r="AD15" s="1">
-        <f t="shared" si="17"/>
-        <v>1.6666666666666665</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="AE15" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>3</v>
       </c>
       <c r="AF15" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="AG15" s="1">
-        <f t="shared" si="20"/>
-        <v>1.2222222222222221</v>
+        <f t="shared" si="11"/>
+        <v>3.3333333333333335</v>
       </c>
     </row>
     <row r="16" spans="1:35">
@@ -3775,16 +3772,16 @@
         <v>61</v>
       </c>
       <c r="C16" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="15">
         <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>41</v>
@@ -3793,861 +3790,861 @@
         <v>46127</v>
       </c>
       <c r="I16" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="J16" s="1">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1">
+        <v>1</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>1</v>
+      </c>
+      <c r="R16" s="1">
+        <v>0</v>
+      </c>
+      <c r="S16" s="1">
+        <v>0</v>
+      </c>
+      <c r="T16" s="1">
+        <v>0</v>
+      </c>
+      <c r="U16" s="1">
+        <v>0</v>
+      </c>
+      <c r="V16" s="1">
+        <v>0</v>
+      </c>
+      <c r="W16" s="1">
+        <v>0</v>
+      </c>
+      <c r="X16" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="22">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="1">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AA16" s="1">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="AB16" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="AC16" s="1">
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="J16" s="1">
-        <v>1</v>
-      </c>
-      <c r="K16" s="1">
-        <v>1</v>
-      </c>
-      <c r="L16" s="1">
-        <v>1</v>
-      </c>
-      <c r="M16" s="1">
-        <v>1</v>
-      </c>
-      <c r="N16" s="1">
-        <v>1</v>
-      </c>
-      <c r="O16" s="1">
-        <v>1</v>
-      </c>
-      <c r="P16" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>1</v>
-      </c>
-      <c r="R16" s="1">
-        <v>1</v>
-      </c>
-      <c r="S16" s="1">
-        <v>0</v>
-      </c>
-      <c r="T16" s="1">
-        <v>1</v>
-      </c>
-      <c r="U16" s="1">
-        <v>1</v>
-      </c>
-      <c r="V16" s="1">
-        <v>1</v>
-      </c>
-      <c r="W16" s="1">
-        <v>0</v>
-      </c>
-      <c r="X16" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="22">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="1">
-        <f t="shared" si="13"/>
-        <v>6</v>
-      </c>
-      <c r="AA16" s="1">
+      <c r="AD16" s="1">
+        <f t="shared" si="8"/>
+        <v>1.6666666666666665</v>
+      </c>
+      <c r="AE16" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AF16" s="1">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AG16" s="1">
+        <f t="shared" si="11"/>
+        <v>1.2222222222222221</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33">
+      <c r="A17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="15">
+        <v>1</v>
+      </c>
+      <c r="D17" s="15">
+        <v>1</v>
+      </c>
+      <c r="E17" s="15">
+        <v>0</v>
+      </c>
+      <c r="F17" s="15">
+        <v>2</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17" s="27">
+        <v>46128</v>
+      </c>
+      <c r="I17" s="1">
+        <v>3</v>
+      </c>
+      <c r="J17" s="1">
+        <v>1</v>
+      </c>
+      <c r="K17" s="1">
+        <v>1</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>1</v>
+      </c>
+      <c r="N17" s="1">
+        <v>1</v>
+      </c>
+      <c r="O17" s="1">
+        <v>1</v>
+      </c>
+      <c r="P17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>0</v>
+      </c>
+      <c r="R17" s="1">
+        <v>1</v>
+      </c>
+      <c r="S17" s="1">
+        <v>0</v>
+      </c>
+      <c r="T17" s="1">
+        <v>0</v>
+      </c>
+      <c r="U17" s="1">
+        <v>1</v>
+      </c>
+      <c r="V17" s="1">
+        <v>1</v>
+      </c>
+      <c r="W17" s="1">
+        <v>0</v>
+      </c>
+      <c r="X17" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="1">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="AA17" s="1">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="AB17" s="1">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AC17" s="1">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="AD17" s="1">
+        <f t="shared" si="8"/>
+        <v>4.166666666666667</v>
+      </c>
+      <c r="AE17" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AF17" s="1">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="AG17" s="1">
+        <f t="shared" si="11"/>
+        <v>3.0555555555555558</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33">
+      <c r="A18" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="15">
+        <v>9</v>
+      </c>
+      <c r="D18" s="15">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>0</v>
+      </c>
+      <c r="F18" s="15">
+        <v>2</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H18" s="27">
+        <v>46128</v>
+      </c>
+      <c r="I18" s="1">
+        <v>2</v>
+      </c>
+      <c r="J18" s="1">
+        <v>1</v>
+      </c>
+      <c r="K18" s="1">
+        <v>1</v>
+      </c>
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1">
+        <v>1</v>
+      </c>
+      <c r="O18" s="1">
+        <v>1</v>
+      </c>
+      <c r="P18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>0</v>
+      </c>
+      <c r="R18" s="1">
+        <v>1</v>
+      </c>
+      <c r="S18" s="1">
+        <v>0</v>
+      </c>
+      <c r="T18" s="1">
+        <v>0</v>
+      </c>
+      <c r="U18" s="1">
+        <v>0</v>
+      </c>
+      <c r="V18" s="1">
+        <v>1</v>
+      </c>
+      <c r="W18" s="1">
+        <v>0</v>
+      </c>
+      <c r="X18" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="1">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="AA18" s="1">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="AB18" s="1">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="AC18" s="1">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="AD18" s="1">
+        <f t="shared" si="8"/>
+        <v>4.166666666666667</v>
+      </c>
+      <c r="AE18" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AF18" s="1">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="AG18" s="1">
+        <f t="shared" si="11"/>
+        <v>2.7222222222222228</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33">
+      <c r="A19" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="15">
+        <v>8</v>
+      </c>
+      <c r="D19" s="15">
+        <v>1</v>
+      </c>
+      <c r="E19" s="15">
+        <v>0</v>
+      </c>
+      <c r="F19" s="15">
+        <v>2</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H19" s="27">
+        <v>46128</v>
+      </c>
+      <c r="I19" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="J19" s="1">
+        <v>1</v>
+      </c>
+      <c r="K19" s="1">
+        <v>1</v>
+      </c>
+      <c r="L19" s="1">
+        <v>1</v>
+      </c>
+      <c r="M19" s="1">
+        <v>1</v>
+      </c>
+      <c r="N19" s="22">
+        <v>1</v>
+      </c>
+      <c r="O19" s="1">
+        <v>0</v>
+      </c>
+      <c r="P19" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="22">
+        <v>1</v>
+      </c>
+      <c r="R19" s="22">
+        <v>1</v>
+      </c>
+      <c r="S19" s="1">
+        <v>0</v>
+      </c>
+      <c r="T19" s="1">
+        <v>1</v>
+      </c>
+      <c r="U19" s="22">
+        <v>1</v>
+      </c>
+      <c r="V19" s="1">
+        <v>1</v>
+      </c>
+      <c r="W19" s="22">
+        <v>0</v>
+      </c>
+      <c r="X19" s="22">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="1">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="AA19" s="1">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="AB19" s="1">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="AC19" s="1">
+        <f t="shared" si="7"/>
+        <v>12</v>
+      </c>
+      <c r="AD19" s="1">
+        <f t="shared" si="8"/>
+        <v>4.166666666666667</v>
+      </c>
+      <c r="AE19" s="1">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="AF19" s="1">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="AG19" s="1">
+        <f t="shared" si="11"/>
+        <v>3.7222222222222228</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33">
+      <c r="A20" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="15">
+        <v>11</v>
+      </c>
+      <c r="D20" s="15">
+        <v>0</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
+      </c>
+      <c r="F20" s="15">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H20" s="27">
+        <v>46128</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="J20" s="1">
+        <v>1</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0</v>
+      </c>
+      <c r="M20" s="1">
+        <v>0</v>
+      </c>
+      <c r="N20" s="1">
+        <v>0</v>
+      </c>
+      <c r="O20" s="1">
+        <v>0</v>
+      </c>
+      <c r="P20" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>1</v>
+      </c>
+      <c r="R20" s="1">
+        <v>0</v>
+      </c>
+      <c r="S20" s="1">
+        <v>0</v>
+      </c>
+      <c r="T20" s="1">
+        <v>0</v>
+      </c>
+      <c r="U20" s="1">
+        <v>0</v>
+      </c>
+      <c r="V20" s="1">
+        <v>0</v>
+      </c>
+      <c r="W20" s="1">
+        <v>0</v>
+      </c>
+      <c r="X20" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AA20" s="1">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="AB20" s="1">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AC20" s="1">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="AD20" s="1">
+        <f t="shared" si="8"/>
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="AE20" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AF20" s="1">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AG20" s="1">
+        <f t="shared" si="11"/>
+        <v>1.2777777777777777</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33">
+      <c r="A21" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" s="15">
+        <v>7</v>
+      </c>
+      <c r="D21" s="15">
+        <v>0</v>
+      </c>
+      <c r="E21" s="15">
+        <v>0</v>
+      </c>
+      <c r="F21" s="15">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H21" s="27">
+        <v>46128</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="J21" s="1">
+        <v>1</v>
+      </c>
+      <c r="K21" s="1">
+        <v>1</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0</v>
+      </c>
+      <c r="O21" s="1">
+        <v>0</v>
+      </c>
+      <c r="P21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>1</v>
+      </c>
+      <c r="R21" s="1">
+        <v>0</v>
+      </c>
+      <c r="S21" s="1">
+        <v>0</v>
+      </c>
+      <c r="T21" s="1">
+        <v>0</v>
+      </c>
+      <c r="U21" s="1">
+        <v>0</v>
+      </c>
+      <c r="V21" s="1">
+        <v>0</v>
+      </c>
+      <c r="W21" s="1">
+        <v>0</v>
+      </c>
+      <c r="X21" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="22">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="1">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AA21" s="1">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="AB21" s="1">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="AC21" s="1">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="AD21" s="1">
+        <f t="shared" si="8"/>
+        <v>1.6666666666666665</v>
+      </c>
+      <c r="AE21" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AF21" s="1">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AG21" s="1">
+        <f t="shared" si="11"/>
+        <v>1.2222222222222221</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33">
+      <c r="A22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="15">
+        <v>19</v>
+      </c>
+      <c r="D22" s="15">
+        <v>0</v>
+      </c>
+      <c r="E22" s="15">
+        <v>0</v>
+      </c>
+      <c r="F22" s="15">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H22" s="27">
+        <v>46128</v>
+      </c>
+      <c r="I22" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="J22" s="1">
+        <v>1</v>
+      </c>
+      <c r="K22" s="1">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1">
+        <v>0</v>
+      </c>
+      <c r="N22" s="1">
+        <v>0</v>
+      </c>
+      <c r="O22" s="1">
+        <v>0</v>
+      </c>
+      <c r="P22" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>1</v>
+      </c>
+      <c r="R22" s="1">
+        <v>0</v>
+      </c>
+      <c r="S22" s="1">
+        <v>0</v>
+      </c>
+      <c r="T22" s="1">
+        <v>0</v>
+      </c>
+      <c r="U22" s="1">
+        <v>0</v>
+      </c>
+      <c r="V22" s="1">
+        <v>0</v>
+      </c>
+      <c r="W22" s="1">
+        <v>0</v>
+      </c>
+      <c r="X22" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="1">
+        <f t="shared" ref="Z22:Z24" si="12">SUM(J22:O22)</f>
+        <v>1</v>
+      </c>
+      <c r="AA22" s="1">
+        <f t="shared" ref="AA22" si="13">SUM(P22:T22)</f>
+        <v>1</v>
+      </c>
+      <c r="AB22" s="1">
+        <f t="shared" ref="AB22:AB26" si="14">SUM(U22:Y22)</f>
+        <v>2</v>
+      </c>
+      <c r="AC22" s="1">
+        <f t="shared" ref="AC22:AC26" si="15">SUM(Z22:AB22)</f>
+        <v>4</v>
+      </c>
+      <c r="AD22" s="1">
+        <f>Z22/6*5</f>
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="AE22" s="1">
+        <f>AA22/5*5</f>
+        <v>1</v>
+      </c>
+      <c r="AF22" s="1">
+        <f xml:space="preserve"> AB22/5*5</f>
+        <v>2</v>
+      </c>
+      <c r="AG22" s="1">
+        <f>SUM(AD22:AF22)/3</f>
+        <v>1.2777777777777777</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33">
+      <c r="A23" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="15">
+        <v>5</v>
+      </c>
+      <c r="D23" s="15">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>0</v>
+      </c>
+      <c r="F23" s="15">
+        <v>2</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H23" s="27">
+        <v>46129</v>
+      </c>
+      <c r="I23" s="1">
+        <v>2</v>
+      </c>
+      <c r="J23" s="1">
+        <v>1</v>
+      </c>
+      <c r="K23" s="1">
+        <v>1</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1</v>
+      </c>
+      <c r="M23" s="1">
+        <v>0</v>
+      </c>
+      <c r="N23" s="1">
+        <v>1</v>
+      </c>
+      <c r="O23" s="1">
+        <v>1</v>
+      </c>
+      <c r="P23" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>1</v>
+      </c>
+      <c r="R23" s="1">
+        <v>1</v>
+      </c>
+      <c r="S23" s="1">
+        <v>0</v>
+      </c>
+      <c r="T23" s="1">
+        <v>0</v>
+      </c>
+      <c r="U23" s="1">
+        <v>1</v>
+      </c>
+      <c r="V23" s="1">
+        <v>1</v>
+      </c>
+      <c r="W23" s="1">
+        <v>0</v>
+      </c>
+      <c r="X23" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="22">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="1">
+        <f t="shared" si="12"/>
+        <v>5</v>
+      </c>
+      <c r="AA23" s="1">
+        <f>SUM(P23:T23)</f>
+        <v>2</v>
+      </c>
+      <c r="AB23" s="1">
         <f t="shared" si="14"/>
         <v>3</v>
       </c>
-      <c r="AB16" s="1">
+      <c r="AC23" s="1">
         <f t="shared" si="15"/>
-        <v>2</v>
-      </c>
-      <c r="AC16" s="1">
-        <f t="shared" si="16"/>
-        <v>11</v>
-      </c>
-      <c r="AD16" s="1">
-        <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="AE16" s="1">
-        <f t="shared" si="18"/>
+        <v>10</v>
+      </c>
+      <c r="AD23" s="1">
+        <f>Z23/6*5</f>
+        <v>4.166666666666667</v>
+      </c>
+      <c r="AE23" s="1">
+        <f>AA23/5*5</f>
+        <v>2</v>
+      </c>
+      <c r="AF23" s="1">
+        <f xml:space="preserve"> AB23/5*5</f>
         <v>3</v>
       </c>
-      <c r="AF16" s="1">
-        <f t="shared" si="19"/>
-        <v>2</v>
-      </c>
-      <c r="AG16" s="1">
-        <f t="shared" si="20"/>
-        <v>3.3333333333333335</v>
-      </c>
-    </row>
-    <row r="17" spans="1:33">
-      <c r="A17" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" s="15">
-        <v>1</v>
-      </c>
-      <c r="D17" s="15">
-        <v>0</v>
-      </c>
-      <c r="E17" s="15">
-        <v>0</v>
-      </c>
-      <c r="F17" s="15">
-        <v>1</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H17" s="27">
-        <v>46127</v>
-      </c>
-      <c r="I17" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="J17" s="1">
-        <v>1</v>
-      </c>
-      <c r="K17" s="1">
-        <v>1</v>
-      </c>
-      <c r="L17" s="1">
-        <v>0</v>
-      </c>
-      <c r="M17" s="1">
-        <v>0</v>
-      </c>
-      <c r="N17" s="1">
-        <v>0</v>
-      </c>
-      <c r="O17" s="1">
-        <v>0</v>
-      </c>
-      <c r="P17" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="1">
-        <v>1</v>
-      </c>
-      <c r="R17" s="1">
-        <v>0</v>
-      </c>
-      <c r="S17" s="1">
-        <v>0</v>
-      </c>
-      <c r="T17" s="1">
-        <v>0</v>
-      </c>
-      <c r="U17" s="1">
-        <v>0</v>
-      </c>
-      <c r="V17" s="1">
-        <v>0</v>
-      </c>
-      <c r="W17" s="1">
-        <v>0</v>
-      </c>
-      <c r="X17" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y17" s="22">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="1">
-        <f t="shared" si="13"/>
-        <v>2</v>
-      </c>
-      <c r="AA17" s="1">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="AB17" s="1">
-        <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-      <c r="AC17" s="1">
-        <f t="shared" si="16"/>
-        <v>4</v>
-      </c>
-      <c r="AD17" s="1">
-        <f t="shared" si="17"/>
-        <v>1.6666666666666665</v>
-      </c>
-      <c r="AE17" s="1">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-      <c r="AF17" s="1">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="AG17" s="1">
-        <f t="shared" si="20"/>
-        <v>1.2222222222222221</v>
-      </c>
-    </row>
-    <row r="18" spans="1:33">
-      <c r="A18" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" s="15">
-        <v>1</v>
-      </c>
-      <c r="D18" s="15">
-        <v>1</v>
-      </c>
-      <c r="E18" s="15">
-        <v>0</v>
-      </c>
-      <c r="F18" s="15">
-        <v>2</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H18" s="27">
-        <v>46128</v>
-      </c>
-      <c r="I18" s="1">
-        <v>3</v>
-      </c>
-      <c r="J18" s="1">
-        <v>1</v>
-      </c>
-      <c r="K18" s="1">
-        <v>1</v>
-      </c>
-      <c r="L18" s="1">
-        <v>0</v>
-      </c>
-      <c r="M18" s="1">
-        <v>1</v>
-      </c>
-      <c r="N18" s="1">
-        <v>1</v>
-      </c>
-      <c r="O18" s="1">
-        <v>1</v>
-      </c>
-      <c r="P18" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="1">
-        <v>0</v>
-      </c>
-      <c r="R18" s="1">
-        <v>1</v>
-      </c>
-      <c r="S18" s="1">
-        <v>0</v>
-      </c>
-      <c r="T18" s="1">
-        <v>0</v>
-      </c>
-      <c r="U18" s="1">
-        <v>1</v>
-      </c>
-      <c r="V18" s="1">
-        <v>1</v>
-      </c>
-      <c r="W18" s="1">
-        <v>0</v>
-      </c>
-      <c r="X18" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y18" s="22">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="1">
-        <f t="shared" si="13"/>
-        <v>5</v>
-      </c>
-      <c r="AA18" s="1">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="AB18" s="1">
-        <f t="shared" si="15"/>
-        <v>4</v>
-      </c>
-      <c r="AC18" s="1">
-        <f t="shared" si="16"/>
-        <v>10</v>
-      </c>
-      <c r="AD18" s="1">
-        <f t="shared" si="17"/>
-        <v>4.166666666666667</v>
-      </c>
-      <c r="AE18" s="1">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-      <c r="AF18" s="1">
-        <f t="shared" si="19"/>
-        <v>4</v>
-      </c>
-      <c r="AG18" s="1">
-        <f t="shared" si="20"/>
+      <c r="AG23" s="1">
+        <f>SUM(AD23:AF23)/3</f>
         <v>3.0555555555555558</v>
-      </c>
-    </row>
-    <row r="19" spans="1:33">
-      <c r="A19" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="15">
-        <v>9</v>
-      </c>
-      <c r="D19" s="15">
-        <v>1</v>
-      </c>
-      <c r="E19" s="15">
-        <v>0</v>
-      </c>
-      <c r="F19" s="15">
-        <v>2</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H19" s="27">
-        <v>46128</v>
-      </c>
-      <c r="I19" s="1">
-        <v>2</v>
-      </c>
-      <c r="J19" s="1">
-        <v>1</v>
-      </c>
-      <c r="K19" s="1">
-        <v>1</v>
-      </c>
-      <c r="L19" s="1">
-        <v>1</v>
-      </c>
-      <c r="M19" s="1">
-        <v>0</v>
-      </c>
-      <c r="N19" s="1">
-        <v>1</v>
-      </c>
-      <c r="O19" s="1">
-        <v>1</v>
-      </c>
-      <c r="P19" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="1">
-        <v>0</v>
-      </c>
-      <c r="R19" s="1">
-        <v>1</v>
-      </c>
-      <c r="S19" s="1">
-        <v>0</v>
-      </c>
-      <c r="T19" s="1">
-        <v>0</v>
-      </c>
-      <c r="U19" s="1">
-        <v>0</v>
-      </c>
-      <c r="V19" s="1">
-        <v>1</v>
-      </c>
-      <c r="W19" s="1">
-        <v>0</v>
-      </c>
-      <c r="X19" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y19" s="22">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="1">
-        <f t="shared" si="13"/>
-        <v>5</v>
-      </c>
-      <c r="AA19" s="1">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="AB19" s="1">
-        <f t="shared" si="15"/>
-        <v>3</v>
-      </c>
-      <c r="AC19" s="1">
-        <f t="shared" si="16"/>
-        <v>9</v>
-      </c>
-      <c r="AD19" s="1">
-        <f t="shared" si="17"/>
-        <v>4.166666666666667</v>
-      </c>
-      <c r="AE19" s="1">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-      <c r="AF19" s="1">
-        <f t="shared" si="19"/>
-        <v>3</v>
-      </c>
-      <c r="AG19" s="1">
-        <f t="shared" si="20"/>
-        <v>2.7222222222222228</v>
-      </c>
-    </row>
-    <row r="20" spans="1:33">
-      <c r="A20" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="15">
-        <v>8</v>
-      </c>
-      <c r="D20" s="15">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>0</v>
-      </c>
-      <c r="F20" s="15">
-        <v>2</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H20" s="27">
-        <v>46128</v>
-      </c>
-      <c r="I20" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="J20" s="1">
-        <v>1</v>
-      </c>
-      <c r="K20" s="1">
-        <v>1</v>
-      </c>
-      <c r="L20" s="1">
-        <v>1</v>
-      </c>
-      <c r="M20" s="1">
-        <v>1</v>
-      </c>
-      <c r="N20" s="22">
-        <v>1</v>
-      </c>
-      <c r="O20" s="1">
-        <v>0</v>
-      </c>
-      <c r="P20" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="22">
-        <v>1</v>
-      </c>
-      <c r="R20" s="22">
-        <v>1</v>
-      </c>
-      <c r="S20" s="1">
-        <v>0</v>
-      </c>
-      <c r="T20" s="1">
-        <v>1</v>
-      </c>
-      <c r="U20" s="22">
-        <v>1</v>
-      </c>
-      <c r="V20" s="1">
-        <v>1</v>
-      </c>
-      <c r="W20" s="22">
-        <v>0</v>
-      </c>
-      <c r="X20" s="22">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="22">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="1">
-        <f t="shared" si="13"/>
-        <v>5</v>
-      </c>
-      <c r="AA20" s="1">
-        <f t="shared" si="14"/>
-        <v>4</v>
-      </c>
-      <c r="AB20" s="1">
-        <f t="shared" si="15"/>
-        <v>3</v>
-      </c>
-      <c r="AC20" s="1">
-        <f t="shared" si="16"/>
-        <v>12</v>
-      </c>
-      <c r="AD20" s="1">
-        <f t="shared" si="17"/>
-        <v>4.166666666666667</v>
-      </c>
-      <c r="AE20" s="1">
-        <f t="shared" si="18"/>
-        <v>4</v>
-      </c>
-      <c r="AF20" s="1">
-        <f t="shared" si="19"/>
-        <v>3</v>
-      </c>
-      <c r="AG20" s="1">
-        <f t="shared" si="20"/>
-        <v>3.7222222222222228</v>
-      </c>
-    </row>
-    <row r="21" spans="1:33">
-      <c r="A21" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" s="15">
-        <v>11</v>
-      </c>
-      <c r="D21" s="15">
-        <v>0</v>
-      </c>
-      <c r="E21" s="15">
-        <v>0</v>
-      </c>
-      <c r="F21" s="15">
-        <v>1</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H21" s="27">
-        <v>46128</v>
-      </c>
-      <c r="I21" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="J21" s="1">
-        <v>1</v>
-      </c>
-      <c r="K21" s="1">
-        <v>0</v>
-      </c>
-      <c r="L21" s="1">
-        <v>0</v>
-      </c>
-      <c r="M21" s="1">
-        <v>0</v>
-      </c>
-      <c r="N21" s="1">
-        <v>0</v>
-      </c>
-      <c r="O21" s="1">
-        <v>0</v>
-      </c>
-      <c r="P21" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="1">
-        <v>1</v>
-      </c>
-      <c r="R21" s="1">
-        <v>0</v>
-      </c>
-      <c r="S21" s="1">
-        <v>0</v>
-      </c>
-      <c r="T21" s="1">
-        <v>0</v>
-      </c>
-      <c r="U21" s="1">
-        <v>0</v>
-      </c>
-      <c r="V21" s="1">
-        <v>0</v>
-      </c>
-      <c r="W21" s="1">
-        <v>0</v>
-      </c>
-      <c r="X21" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y21" s="22">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="AA21" s="1">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="AB21" s="1">
-        <f t="shared" si="15"/>
-        <v>2</v>
-      </c>
-      <c r="AC21" s="1">
-        <f t="shared" si="16"/>
-        <v>4</v>
-      </c>
-      <c r="AD21" s="1">
-        <f t="shared" si="17"/>
-        <v>0.83333333333333326</v>
-      </c>
-      <c r="AE21" s="1">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-      <c r="AF21" s="1">
-        <f t="shared" si="19"/>
-        <v>2</v>
-      </c>
-      <c r="AG21" s="1">
-        <f t="shared" si="20"/>
-        <v>1.2777777777777777</v>
-      </c>
-    </row>
-    <row r="22" spans="1:33">
-      <c r="A22" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="15">
-        <v>7</v>
-      </c>
-      <c r="D22" s="15">
-        <v>0</v>
-      </c>
-      <c r="E22" s="15">
-        <v>0</v>
-      </c>
-      <c r="F22" s="15">
-        <v>1</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H22" s="27">
-        <v>46128</v>
-      </c>
-      <c r="I22" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="J22" s="1">
-        <v>1</v>
-      </c>
-      <c r="K22" s="1">
-        <v>1</v>
-      </c>
-      <c r="L22" s="1">
-        <v>0</v>
-      </c>
-      <c r="M22" s="1">
-        <v>0</v>
-      </c>
-      <c r="N22" s="1">
-        <v>0</v>
-      </c>
-      <c r="O22" s="1">
-        <v>0</v>
-      </c>
-      <c r="P22" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="1">
-        <v>1</v>
-      </c>
-      <c r="R22" s="1">
-        <v>0</v>
-      </c>
-      <c r="S22" s="1">
-        <v>0</v>
-      </c>
-      <c r="T22" s="1">
-        <v>0</v>
-      </c>
-      <c r="U22" s="1">
-        <v>0</v>
-      </c>
-      <c r="V22" s="1">
-        <v>0</v>
-      </c>
-      <c r="W22" s="1">
-        <v>0</v>
-      </c>
-      <c r="X22" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y22" s="22">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="1">
-        <f t="shared" si="13"/>
-        <v>2</v>
-      </c>
-      <c r="AA22" s="1">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="AB22" s="1">
-        <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-      <c r="AC22" s="1">
-        <f t="shared" si="16"/>
-        <v>4</v>
-      </c>
-      <c r="AD22" s="1">
-        <f t="shared" si="17"/>
-        <v>1.6666666666666665</v>
-      </c>
-      <c r="AE22" s="1">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-      <c r="AF22" s="1">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="AG22" s="1">
-        <f t="shared" si="20"/>
-        <v>1.2222222222222221</v>
-      </c>
-    </row>
-    <row r="23" spans="1:33">
-      <c r="A23" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C23" s="15">
-        <v>19</v>
-      </c>
-      <c r="D23" s="15">
-        <v>0</v>
-      </c>
-      <c r="E23" s="15">
-        <v>0</v>
-      </c>
-      <c r="F23" s="15">
-        <v>1</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H23" s="27">
-        <v>46128</v>
-      </c>
-      <c r="I23" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="J23" s="1">
-        <v>1</v>
-      </c>
-      <c r="K23" s="1">
-        <v>0</v>
-      </c>
-      <c r="L23" s="1">
-        <v>0</v>
-      </c>
-      <c r="M23" s="1">
-        <v>0</v>
-      </c>
-      <c r="N23" s="1">
-        <v>0</v>
-      </c>
-      <c r="O23" s="1">
-        <v>0</v>
-      </c>
-      <c r="P23" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="1">
-        <v>1</v>
-      </c>
-      <c r="R23" s="1">
-        <v>0</v>
-      </c>
-      <c r="S23" s="1">
-        <v>0</v>
-      </c>
-      <c r="T23" s="1">
-        <v>0</v>
-      </c>
-      <c r="U23" s="1">
-        <v>0</v>
-      </c>
-      <c r="V23" s="1">
-        <v>0</v>
-      </c>
-      <c r="W23" s="1">
-        <v>0</v>
-      </c>
-      <c r="X23" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y23" s="22">
-        <v>1</v>
-      </c>
-      <c r="Z23" s="1">
-        <f t="shared" ref="Z23:Z25" si="21">SUM(J23:O23)</f>
-        <v>1</v>
-      </c>
-      <c r="AA23" s="1">
-        <f t="shared" ref="AA23" si="22">SUM(P23:T23)</f>
-        <v>1</v>
-      </c>
-      <c r="AB23" s="1">
-        <f t="shared" ref="AB23:AB27" si="23">SUM(U23:Y23)</f>
-        <v>2</v>
-      </c>
-      <c r="AC23" s="1">
-        <f t="shared" ref="AC23:AC27" si="24">SUM(Z23:AB23)</f>
-        <v>4</v>
-      </c>
-      <c r="AD23" s="1">
-        <f t="shared" si="5"/>
-        <v>0.83333333333333326</v>
-      </c>
-      <c r="AE23" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AF23" s="1">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="AG23" s="1">
-        <f t="shared" si="7"/>
-        <v>1.2777777777777777</v>
       </c>
     </row>
     <row r="24" spans="1:33">
       <c r="A24" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>72</v>
       </c>
       <c r="C24" s="15">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D24" s="15">
         <v>1</v>
@@ -4659,7 +4656,7 @@
         <v>2</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H24" s="27">
         <v>46129</v>
@@ -4674,7 +4671,7 @@
         <v>1</v>
       </c>
       <c r="L24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="1">
         <v>0</v>
@@ -4683,13 +4680,13 @@
         <v>1</v>
       </c>
       <c r="O24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24" s="1">
         <v>0</v>
       </c>
       <c r="Q24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" s="1">
         <v>1</v>
@@ -4716,47 +4713,47 @@
         <v>0</v>
       </c>
       <c r="Z24" s="1">
-        <f t="shared" si="21"/>
-        <v>5</v>
+        <f t="shared" si="12"/>
+        <v>3</v>
       </c>
       <c r="AA24" s="1">
         <f>SUM(P24:T24)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB24" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
       <c r="AC24" s="1">
-        <f t="shared" si="24"/>
-        <v>10</v>
+        <f t="shared" si="15"/>
+        <v>7</v>
       </c>
       <c r="AD24" s="1">
-        <f t="shared" si="5"/>
-        <v>4.166666666666667</v>
+        <f>Z24/6*5</f>
+        <v>2.5</v>
       </c>
       <c r="AE24" s="1">
-        <f t="shared" si="4"/>
-        <v>2</v>
+        <f>AA24/5*5</f>
+        <v>1</v>
       </c>
       <c r="AF24" s="1">
-        <f t="shared" si="6"/>
+        <f xml:space="preserve"> AB24/5*5</f>
         <v>3</v>
       </c>
       <c r="AG24" s="1">
-        <f t="shared" si="7"/>
-        <v>3.0555555555555558</v>
+        <f>SUM(AD24:AF24)/3</f>
+        <v>2.1666666666666665</v>
       </c>
     </row>
     <row r="25" spans="1:33">
       <c r="A25" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B25" s="15" t="s">
         <v>73</v>
       </c>
       <c r="C25" s="15">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D25" s="15">
         <v>1</v>
@@ -4768,13 +4765,13 @@
         <v>2</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H25" s="27">
         <v>46129</v>
       </c>
       <c r="I25" s="1">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J25" s="1">
         <v>1</v>
@@ -4783,7 +4780,7 @@
         <v>1</v>
       </c>
       <c r="L25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="1">
         <v>0</v>
@@ -4798,7 +4795,7 @@
         <v>0</v>
       </c>
       <c r="Q25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" s="1">
         <v>1</v>
@@ -4819,53 +4816,53 @@
         <v>0</v>
       </c>
       <c r="X25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y25" s="22">
         <v>0</v>
       </c>
       <c r="Z25" s="1">
-        <f t="shared" si="21"/>
-        <v>3</v>
+        <f t="shared" ref="Z25:Z26" si="16">SUM(J25:O25)</f>
+        <v>4</v>
       </c>
       <c r="AA25" s="1">
-        <f>SUM(P25:T25)</f>
-        <v>1</v>
+        <f t="shared" ref="AA25:AA26" si="17">SUM(P25:T25)</f>
+        <v>2</v>
       </c>
       <c r="AB25" s="1">
-        <f t="shared" si="23"/>
-        <v>3</v>
+        <f t="shared" si="14"/>
+        <v>2</v>
       </c>
       <c r="AC25" s="1">
-        <f t="shared" si="24"/>
-        <v>7</v>
+        <f t="shared" si="15"/>
+        <v>8</v>
       </c>
       <c r="AD25" s="1">
-        <f t="shared" si="5"/>
-        <v>2.5</v>
+        <f>Z25/6*5</f>
+        <v>3.333333333333333</v>
       </c>
       <c r="AE25" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f>AA25/5*5</f>
+        <v>2</v>
       </c>
       <c r="AF25" s="1">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f xml:space="preserve"> AB25/5*5</f>
+        <v>2</v>
       </c>
       <c r="AG25" s="1">
-        <f t="shared" si="7"/>
-        <v>2.1666666666666665</v>
+        <f>SUM(AD25:AF25)/3</f>
+        <v>2.4444444444444442</v>
       </c>
     </row>
     <row r="26" spans="1:33">
       <c r="A26" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B26" s="15" t="s">
         <v>74</v>
       </c>
       <c r="C26" s="15">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D26" s="15">
         <v>1</v>
@@ -4877,13 +4874,13 @@
         <v>2</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="H26" s="27">
         <v>46129</v>
       </c>
       <c r="I26" s="1">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J26" s="1">
         <v>1</v>
@@ -4892,22 +4889,22 @@
         <v>1</v>
       </c>
       <c r="L26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" s="1">
         <v>1</v>
       </c>
       <c r="O26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P26" s="1">
         <v>0</v>
       </c>
       <c r="Q26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" s="1">
         <v>1</v>
@@ -4919,7 +4916,7 @@
         <v>0</v>
       </c>
       <c r="U26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="1">
         <v>1</v>
@@ -4928,152 +4925,46 @@
         <v>0</v>
       </c>
       <c r="X26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z26" s="1">
-        <f t="shared" ref="Z26:Z27" si="25">SUM(J26:O26)</f>
-        <v>4</v>
+        <f t="shared" si="16"/>
+        <v>5</v>
       </c>
       <c r="AA26" s="1">
-        <f t="shared" ref="AA26:AA27" si="26">SUM(P26:T26)</f>
-        <v>2</v>
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
       <c r="AB26" s="1">
-        <f t="shared" si="23"/>
-        <v>2</v>
+        <f t="shared" si="14"/>
+        <v>3</v>
       </c>
       <c r="AC26" s="1">
-        <f t="shared" si="24"/>
-        <v>8</v>
+        <f t="shared" si="15"/>
+        <v>9</v>
       </c>
       <c r="AD26" s="1">
-        <f t="shared" si="5"/>
-        <v>3.333333333333333</v>
+        <f>Z26/6*5</f>
+        <v>4.166666666666667</v>
       </c>
       <c r="AE26" s="1">
-        <f t="shared" si="4"/>
-        <v>2</v>
+        <f>AA26/5*5</f>
+        <v>1</v>
       </c>
       <c r="AF26" s="1">
-        <f t="shared" si="6"/>
-        <v>2</v>
+        <f xml:space="preserve"> AB26/5*5</f>
+        <v>3</v>
       </c>
       <c r="AG26" s="1">
-        <f t="shared" si="7"/>
-        <v>2.4444444444444442</v>
+        <f>SUM(AD26:AF26)/3</f>
+        <v>2.7222222222222228</v>
       </c>
     </row>
     <row r="27" spans="1:33">
-      <c r="A27" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" s="15">
-        <v>26</v>
-      </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
-      </c>
-      <c r="F27" s="15">
-        <v>2</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H27" s="27">
-        <v>46129</v>
-      </c>
-      <c r="I27" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="J27" s="1">
-        <v>1</v>
-      </c>
-      <c r="K27" s="1">
-        <v>1</v>
-      </c>
-      <c r="L27" s="1">
-        <v>0</v>
-      </c>
-      <c r="M27" s="1">
-        <v>1</v>
-      </c>
-      <c r="N27" s="1">
-        <v>1</v>
-      </c>
-      <c r="O27" s="1">
-        <v>1</v>
-      </c>
-      <c r="P27" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="1">
-        <v>0</v>
-      </c>
-      <c r="R27" s="1">
-        <v>1</v>
-      </c>
-      <c r="S27" s="1">
-        <v>0</v>
-      </c>
-      <c r="T27" s="1">
-        <v>0</v>
-      </c>
-      <c r="U27" s="1">
-        <v>0</v>
-      </c>
-      <c r="V27" s="1">
-        <v>1</v>
-      </c>
-      <c r="W27" s="1">
-        <v>0</v>
-      </c>
-      <c r="X27" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y27" s="22">
-        <v>1</v>
-      </c>
-      <c r="Z27" s="1">
-        <f t="shared" si="25"/>
-        <v>5</v>
-      </c>
-      <c r="AA27" s="1">
-        <f t="shared" si="26"/>
-        <v>1</v>
-      </c>
-      <c r="AB27" s="1">
-        <f t="shared" si="23"/>
-        <v>3</v>
-      </c>
-      <c r="AC27" s="1">
-        <f t="shared" si="24"/>
-        <v>9</v>
-      </c>
-      <c r="AD27" s="1">
-        <f t="shared" si="5"/>
-        <v>4.166666666666667</v>
-      </c>
-      <c r="AE27" s="1">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AF27" s="1">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="AG27" s="1">
-        <f t="shared" si="7"/>
-        <v>2.7222222222222228</v>
-      </c>
+      <c r="C27" s="15"/>
     </row>
     <row r="28" spans="1:33">
       <c r="C28" s="15"/>
@@ -5162,11 +5053,8 @@
     <row r="56" spans="3:3">
       <c r="C56" s="15"/>
     </row>
-    <row r="57" spans="3:3">
-      <c r="C57" s="15"/>
-    </row>
+    <row r="57" spans="3:3"/>
     <row r="58" spans="3:3"/>
-    <row r="59" spans="3:3"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="J1:O1"/>
@@ -5180,7 +5068,150 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADF0DF9C-6DCA-4063-8046-A184A27D5A8A}">
+  <dimension ref="A1:AI1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:35">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="15">
+        <v>11</v>
+      </c>
+      <c r="D1" s="15">
+        <v>1</v>
+      </c>
+      <c r="E1" s="15">
+        <v>1</v>
+      </c>
+      <c r="F1" s="15">
+        <v>1</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="27">
+        <v>46126</v>
+      </c>
+      <c r="I1" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="J1" s="1">
+        <v>1</v>
+      </c>
+      <c r="K1" s="1">
+        <v>1</v>
+      </c>
+      <c r="L1" s="1">
+        <v>1</v>
+      </c>
+      <c r="M1" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>1</v>
+      </c>
+      <c r="R1" s="22">
+        <v>1</v>
+      </c>
+      <c r="S1" s="1">
+        <v>0</v>
+      </c>
+      <c r="T1" s="1">
+        <v>0</v>
+      </c>
+      <c r="U1" s="1">
+        <v>0</v>
+      </c>
+      <c r="V1" s="1">
+        <v>1</v>
+      </c>
+      <c r="W1" s="1">
+        <v>0</v>
+      </c>
+      <c r="X1" s="22">
+        <v>0</v>
+      </c>
+      <c r="Y1" s="22">
+        <v>0</v>
+      </c>
+      <c r="Z1" s="1">
+        <f>SUM(J1:O1)</f>
+        <v>4</v>
+      </c>
+      <c r="AA1" s="1">
+        <f>SUM(P1:T1)</f>
+        <v>2</v>
+      </c>
+      <c r="AB1" s="1">
+        <f>SUM(U1:Y1)</f>
+        <v>1</v>
+      </c>
+      <c r="AC1" s="1">
+        <f>SUM(Z1:AB1)</f>
+        <v>7</v>
+      </c>
+      <c r="AD1" s="1">
+        <f>Z1/6*5</f>
+        <v>3.333333333333333</v>
+      </c>
+      <c r="AE1" s="1">
+        <f>AA1/5*5</f>
+        <v>2</v>
+      </c>
+      <c r="AF1" s="1">
+        <f xml:space="preserve"> AB1/5*5</f>
+        <v>1</v>
+      </c>
+      <c r="AG1" s="1">
+        <f>SUM(AD1:AF1)/3</f>
+        <v>2.1111111111111112</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI1" s="23"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0278717-252d-455f-9297-341259384352">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="67fd2e6b-9b4b-488b-ae5d-884371a2c380" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006F98E057C991C64EA8C44B2688F4F4E8" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="205ac32a36de600e2ab9bca4f1502e82">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0278717-252d-455f-9297-341259384352" xmlns:ns3="67fd2e6b-9b4b-488b-ae5d-884371a2c380" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="423e538afa53ae88b73bb7a22e6ab62a" ns2:_="" ns3:_="">
     <xsd:import namespace="b0278717-252d-455f-9297-341259384352"/>
@@ -5369,28 +5400,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0278717-252d-455f-9297-341259384352">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="67fd2e6b-9b4b-488b-ae5d-884371a2c380" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32CEAB00-EB88-42CB-8573-B14217434AB6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E6D151-5FDE-4AAE-92E5-7A931745F48E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5398,5 +5409,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E6D151-5FDE-4AAE-92E5-7A931745F48E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32CEAB00-EB88-42CB-8573-B14217434AB6}"/>
 </file>
--- a/Raw/field_UWS.xlsx
+++ b/Raw/field_UWS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mnhnfr.sharepoint.com/sites/ParisWildness/Documents partages/General/Data/UWS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{087AADCE-169F-4340-A908-037967EBD577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D41AA49-51E6-4FCF-8C7F-748084036BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A2E2B354-4CFC-4A8A-96B7-F1F306D34BE6}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="82">
   <si>
     <r>
       <t>Structural complexity</t>
@@ -687,6 +687,9 @@
     <t>48.87939, 2.38529</t>
   </si>
   <si>
+    <t>Sol ciment/stabilisé très limitant : 1 à ant_limiting</t>
+  </si>
+  <si>
     <t>48.87988, 2.39167</t>
   </si>
   <si>
@@ -699,6 +702,9 @@
     <t>48.88451, 2.39577</t>
   </si>
   <si>
+    <t>Topographie : small cracks making a "bosse" so 1</t>
+  </si>
+  <si>
     <t>48.88599, 2.3981</t>
   </si>
   <si>
@@ -726,6 +732,9 @@
     <t>48.87804, 2.40557</t>
   </si>
   <si>
+    <t>Planted  : lot of planted but also lot of spontaneous...</t>
+  </si>
+  <si>
     <t>48.89002, 2.39686</t>
   </si>
   <si>
@@ -738,6 +747,9 @@
     <t>48.87679, 2.38535</t>
   </si>
   <si>
+    <t>Topographie 0 but the vegetalised space if "surélevé"</t>
+  </si>
+  <si>
     <t>48.87498, 2.38588</t>
   </si>
   <si>
@@ -745,6 +757,9 @@
   </si>
   <si>
     <t>48.8489, 2.30459</t>
+  </si>
+  <si>
+    <t>Litter : first 0 but people came to clean the few litter there was, so I put 1</t>
   </si>
   <si>
     <t>48.85007, 2.31233</t>
@@ -1833,8 +1848,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="45262800" y="1009650"/>
-              <a:ext cx="3286125" cy="3228975"/>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2553,6 +2568,9 @@
         <f>SUM(AD4:AF4)/3</f>
         <v>2.4444444444444442</v>
       </c>
+      <c r="AH4" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="AI4" s="23"/>
     </row>
     <row r="5" spans="1:35">
@@ -2560,7 +2578,7 @@
         <v>42</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" s="15">
         <v>11</v>
@@ -2664,7 +2682,7 @@
         <v>1.6111111111111109</v>
       </c>
       <c r="AH5" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:35">
@@ -2672,7 +2690,7 @@
         <v>42</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C6" s="15">
         <v>26</v>
@@ -2781,7 +2799,7 @@
         <v>42</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" s="15">
         <v>17</v>
@@ -2884,6 +2902,9 @@
         <f>SUM(AD7:AF7)/3</f>
         <v>2.5</v>
       </c>
+      <c r="AH7" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="AI7" s="24"/>
     </row>
     <row r="8" spans="1:35">
@@ -2891,7 +2912,7 @@
         <v>42</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C8" s="15">
         <v>30</v>
@@ -2906,7 +2927,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H8" s="27">
         <v>46126</v>
@@ -3001,7 +3022,7 @@
         <v>42</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" s="15">
         <v>20</v>
@@ -3016,7 +3037,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H9" s="27">
         <v>46126</v>
@@ -3111,7 +3132,7 @@
         <v>42</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C10" s="15">
         <v>2</v>
@@ -3221,7 +3242,7 @@
         <v>42</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C11" s="15">
         <v>21</v>
@@ -3236,7 +3257,7 @@
         <v>2</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H11" s="27">
         <v>46127</v>
@@ -3325,7 +3346,7 @@
         <v>3.0555555555555558</v>
       </c>
       <c r="AH11" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:35">
@@ -3333,22 +3354,22 @@
         <v>42</v>
       </c>
       <c r="B12" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="15">
+        <v>33</v>
+      </c>
+      <c r="D12" s="15">
+        <v>1</v>
+      </c>
+      <c r="E12" s="15">
+        <v>0</v>
+      </c>
+      <c r="F12" s="15">
+        <v>2</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C12" s="15">
-        <v>32</v>
-      </c>
-      <c r="D12" s="15">
-        <v>1</v>
-      </c>
-      <c r="E12" s="15">
-        <v>0</v>
-      </c>
-      <c r="F12" s="15">
-        <v>2</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="H12" s="27">
         <v>46127</v>
@@ -3436,13 +3457,16 @@
         <f t="shared" ref="AG12:AG21" si="11">SUM(AD12:AF12)/3</f>
         <v>3.3333333333333335</v>
       </c>
+      <c r="AH12" s="1" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="13" spans="1:35">
       <c r="A13" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C13" s="15">
         <v>27</v>
@@ -3457,7 +3481,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H13" s="27">
         <v>46127</v>
@@ -3551,7 +3575,7 @@
         <v>42</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C14" s="15">
         <v>6</v>
@@ -3566,7 +3590,7 @@
         <v>2</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H14" s="27">
         <v>46127</v>
@@ -3660,7 +3684,7 @@
         <v>42</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C15" s="15">
         <v>4</v>
@@ -3763,13 +3787,16 @@
         <f t="shared" si="11"/>
         <v>3.3333333333333335</v>
       </c>
+      <c r="AH15" s="1" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="16" spans="1:35">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C16" s="15">
         <v>1</v>
@@ -3873,12 +3900,12 @@
         <v>1.2222222222222221</v>
       </c>
     </row>
-    <row r="17" spans="1:33">
+    <row r="17" spans="1:34">
       <c r="A17" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C17" s="15">
         <v>1</v>
@@ -3893,7 +3920,7 @@
         <v>2</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H17" s="27">
         <v>46128</v>
@@ -3981,13 +4008,16 @@
         <f t="shared" si="11"/>
         <v>3.0555555555555558</v>
       </c>
-    </row>
-    <row r="18" spans="1:33">
+      <c r="AH17" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:34">
       <c r="A18" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C18" s="15">
         <v>9</v>
@@ -4002,7 +4032,7 @@
         <v>2</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H18" s="27">
         <v>46128</v>
@@ -4091,12 +4121,12 @@
         <v>2.7222222222222228</v>
       </c>
     </row>
-    <row r="19" spans="1:33">
+    <row r="19" spans="1:34">
       <c r="A19" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C19" s="15">
         <v>8</v>
@@ -4111,7 +4141,7 @@
         <v>2</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H19" s="27">
         <v>46128</v>
@@ -4200,12 +4230,12 @@
         <v>3.7222222222222228</v>
       </c>
     </row>
-    <row r="20" spans="1:33">
+    <row r="20" spans="1:34">
       <c r="A20" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C20" s="15">
         <v>11</v>
@@ -4220,7 +4250,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H20" s="27">
         <v>46128</v>
@@ -4309,12 +4339,12 @@
         <v>1.2777777777777777</v>
       </c>
     </row>
-    <row r="21" spans="1:33">
+    <row r="21" spans="1:34">
       <c r="A21" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C21" s="15">
         <v>7</v>
@@ -4418,12 +4448,12 @@
         <v>1.2222222222222221</v>
       </c>
     </row>
-    <row r="22" spans="1:33">
+    <row r="22" spans="1:34">
       <c r="A22" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C22" s="15">
         <v>19</v>
@@ -4438,7 +4468,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H22" s="27">
         <v>46128</v>
@@ -4527,12 +4557,12 @@
         <v>1.2777777777777777</v>
       </c>
     </row>
-    <row r="23" spans="1:33">
+    <row r="23" spans="1:34">
       <c r="A23" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C23" s="15">
         <v>5</v>
@@ -4547,7 +4577,7 @@
         <v>2</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H23" s="27">
         <v>46129</v>
@@ -4636,12 +4666,12 @@
         <v>3.0555555555555558</v>
       </c>
     </row>
-    <row r="24" spans="1:33">
+    <row r="24" spans="1:34">
       <c r="A24" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C24" s="15">
         <v>25</v>
@@ -4656,7 +4686,7 @@
         <v>2</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H24" s="27">
         <v>46129</v>
@@ -4745,12 +4775,12 @@
         <v>2.1666666666666665</v>
       </c>
     </row>
-    <row r="25" spans="1:33">
+    <row r="25" spans="1:34">
       <c r="A25" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C25" s="15">
         <v>27</v>
@@ -4765,7 +4795,7 @@
         <v>2</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H25" s="27">
         <v>46129</v>
@@ -4854,12 +4884,12 @@
         <v>2.4444444444444442</v>
       </c>
     </row>
-    <row r="26" spans="1:33">
+    <row r="26" spans="1:34">
       <c r="A26" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C26" s="15">
         <v>26</v>
@@ -4874,7 +4904,7 @@
         <v>2</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H26" s="27">
         <v>46129</v>
@@ -4963,22 +4993,22 @@
         <v>2.7222222222222228</v>
       </c>
     </row>
-    <row r="27" spans="1:33">
+    <row r="27" spans="1:34">
       <c r="C27" s="15"/>
     </row>
-    <row r="28" spans="1:33">
+    <row r="28" spans="1:34">
       <c r="C28" s="15"/>
     </row>
-    <row r="29" spans="1:33">
+    <row r="29" spans="1:34">
       <c r="C29" s="15"/>
     </row>
-    <row r="30" spans="1:33">
+    <row r="30" spans="1:34">
       <c r="C30" s="15"/>
     </row>
-    <row r="31" spans="1:33">
+    <row r="31" spans="1:34">
       <c r="C31" s="15"/>
     </row>
-    <row r="32" spans="1:33">
+    <row r="32" spans="1:34">
       <c r="C32" s="15"/>
     </row>
     <row r="33" spans="3:3">
@@ -5078,7 +5108,7 @@
         <v>42</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C1" s="15">
         <v>11</v>
@@ -5182,7 +5212,7 @@
         <v>2.1111111111111112</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI1" s="23"/>
     </row>

--- a/Raw/field_UWS.xlsx
+++ b/Raw/field_UWS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mnhnfr.sharepoint.com/sites/ParisWildness/Documents partages/General/Data/UWS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D41AA49-51E6-4FCF-8C7F-748084036BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{00C45CF5-0095-4B8A-B80D-4373C65739AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A2E2B354-4CFC-4A8A-96B7-F1F306D34BE6}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="94">
   <si>
     <r>
       <t>Structural complexity</t>
@@ -796,6 +796,42 @@
   </si>
   <si>
     <t>Parc</t>
+  </si>
+  <si>
+    <t>48.86175, 2.3045</t>
+  </si>
+  <si>
+    <t>cognac</t>
+  </si>
+  <si>
+    <t>48.8608, 2.32009</t>
+  </si>
+  <si>
+    <t>Courty</t>
+  </si>
+  <si>
+    <t>48.85862, 2.32703</t>
+  </si>
+  <si>
+    <t>verneuil</t>
+  </si>
+  <si>
+    <t>48.85674, 2.32744</t>
+  </si>
+  <si>
+    <t>Montalembert</t>
+  </si>
+  <si>
+    <t>48.88622, 2.3799</t>
+  </si>
+  <si>
+    <t>Tandou</t>
+  </si>
+  <si>
+    <t>48.88326, 2.37388</t>
+  </si>
+  <si>
+    <t>Lally</t>
   </si>
   <si>
     <t>avec liane</t>
@@ -4994,22 +5030,658 @@
       </c>
     </row>
     <row r="27" spans="1:34">
-      <c r="C27" s="15"/>
+      <c r="A27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
+      </c>
+      <c r="F27" s="15">
+        <v>2</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H27" s="27">
+        <v>46140</v>
+      </c>
+      <c r="I27" s="1">
+        <v>3</v>
+      </c>
+      <c r="J27" s="1">
+        <v>1</v>
+      </c>
+      <c r="K27" s="1">
+        <v>1</v>
+      </c>
+      <c r="L27" s="1">
+        <v>1</v>
+      </c>
+      <c r="M27" s="1">
+        <v>0</v>
+      </c>
+      <c r="N27" s="1">
+        <v>1</v>
+      </c>
+      <c r="O27" s="1">
+        <v>1</v>
+      </c>
+      <c r="P27" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>0</v>
+      </c>
+      <c r="R27" s="1">
+        <v>1</v>
+      </c>
+      <c r="S27" s="1">
+        <v>0</v>
+      </c>
+      <c r="T27" s="1">
+        <v>1</v>
+      </c>
+      <c r="U27" s="1">
+        <v>1</v>
+      </c>
+      <c r="V27" s="1">
+        <v>1</v>
+      </c>
+      <c r="W27" s="1">
+        <v>0</v>
+      </c>
+      <c r="X27" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="22">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="1">
+        <f t="shared" ref="Z27:Z32" si="18">SUM(J27:O27)</f>
+        <v>5</v>
+      </c>
+      <c r="AA27" s="1">
+        <f t="shared" ref="AA27:AA32" si="19">SUM(P27:T27)</f>
+        <v>2</v>
+      </c>
+      <c r="AB27" s="1">
+        <f t="shared" ref="AB27:AB32" si="20">SUM(U27:Y27)</f>
+        <v>2</v>
+      </c>
+      <c r="AC27" s="1">
+        <f t="shared" ref="AC27:AC32" si="21">SUM(Z27:AB27)</f>
+        <v>9</v>
+      </c>
+      <c r="AD27" s="1">
+        <f t="shared" ref="AD27:AD32" si="22">Z27/6*5</f>
+        <v>4.166666666666667</v>
+      </c>
+      <c r="AE27" s="1">
+        <f t="shared" ref="AE27:AE32" si="23">AA27/5*5</f>
+        <v>2</v>
+      </c>
+      <c r="AF27" s="1">
+        <f t="shared" ref="AF27:AF32" si="24" xml:space="preserve"> AB27/5*5</f>
+        <v>2</v>
+      </c>
+      <c r="AG27" s="1">
+        <f t="shared" ref="AG27:AG32" si="25">SUM(AD27:AF27)/3</f>
+        <v>2.7222222222222228</v>
+      </c>
     </row>
     <row r="28" spans="1:34">
-      <c r="C28" s="15"/>
+      <c r="A28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="D28" s="15">
+        <v>0</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
+      </c>
+      <c r="F28" s="15">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H28" s="27">
+        <v>46140</v>
+      </c>
+      <c r="I28" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="J28" s="1">
+        <v>1</v>
+      </c>
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1">
+        <v>0</v>
+      </c>
+      <c r="N28" s="1">
+        <v>0</v>
+      </c>
+      <c r="O28" s="1">
+        <v>0</v>
+      </c>
+      <c r="P28" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>1</v>
+      </c>
+      <c r="R28" s="1">
+        <v>0</v>
+      </c>
+      <c r="S28" s="1">
+        <v>0</v>
+      </c>
+      <c r="T28" s="1">
+        <v>0</v>
+      </c>
+      <c r="U28" s="1">
+        <v>0</v>
+      </c>
+      <c r="V28" s="1">
+        <v>0</v>
+      </c>
+      <c r="W28" s="1">
+        <v>0</v>
+      </c>
+      <c r="X28" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y28" s="22">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="1">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="AA28" s="1">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AB28" s="1">
+        <f t="shared" si="20"/>
+        <v>1</v>
+      </c>
+      <c r="AC28" s="1">
+        <f t="shared" si="21"/>
+        <v>3</v>
+      </c>
+      <c r="AD28" s="1">
+        <f t="shared" si="22"/>
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="AE28" s="1">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="AF28" s="1">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="AG28" s="1">
+        <f t="shared" si="25"/>
+        <v>0.94444444444444431</v>
+      </c>
     </row>
     <row r="29" spans="1:34">
-      <c r="C29" s="15"/>
+      <c r="A29" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" s="15">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>0</v>
+      </c>
+      <c r="F29" s="15">
+        <v>2</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H29" s="27">
+        <v>46140</v>
+      </c>
+      <c r="I29" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="J29" s="1">
+        <v>1</v>
+      </c>
+      <c r="K29" s="1">
+        <v>1</v>
+      </c>
+      <c r="L29" s="1">
+        <v>1</v>
+      </c>
+      <c r="M29" s="1">
+        <v>0</v>
+      </c>
+      <c r="N29" s="1">
+        <v>1</v>
+      </c>
+      <c r="O29" s="1">
+        <v>1</v>
+      </c>
+      <c r="P29" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>0</v>
+      </c>
+      <c r="R29" s="1">
+        <v>1</v>
+      </c>
+      <c r="S29" s="1">
+        <v>0</v>
+      </c>
+      <c r="T29" s="1">
+        <v>0</v>
+      </c>
+      <c r="U29" s="1">
+        <v>1</v>
+      </c>
+      <c r="V29" s="1">
+        <v>1</v>
+      </c>
+      <c r="W29" s="1">
+        <v>0</v>
+      </c>
+      <c r="X29" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="22">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="1">
+        <f t="shared" si="18"/>
+        <v>5</v>
+      </c>
+      <c r="AA29" s="1">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AB29" s="1">
+        <f t="shared" si="20"/>
+        <v>2</v>
+      </c>
+      <c r="AC29" s="1">
+        <f t="shared" si="21"/>
+        <v>8</v>
+      </c>
+      <c r="AD29" s="1">
+        <f t="shared" si="22"/>
+        <v>4.166666666666667</v>
+      </c>
+      <c r="AE29" s="1">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="AF29" s="1">
+        <f t="shared" si="24"/>
+        <v>2</v>
+      </c>
+      <c r="AG29" s="1">
+        <f t="shared" si="25"/>
+        <v>2.3888888888888888</v>
+      </c>
     </row>
     <row r="30" spans="1:34">
-      <c r="C30" s="15"/>
+      <c r="A30" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30" s="15">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
+      </c>
+      <c r="F30" s="15">
+        <v>2</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H30" s="27">
+        <v>46140</v>
+      </c>
+      <c r="I30" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="J30" s="1">
+        <v>1</v>
+      </c>
+      <c r="K30" s="1">
+        <v>1</v>
+      </c>
+      <c r="L30" s="1">
+        <v>1</v>
+      </c>
+      <c r="M30" s="1">
+        <v>0</v>
+      </c>
+      <c r="N30" s="1">
+        <v>1</v>
+      </c>
+      <c r="O30" s="1">
+        <v>1</v>
+      </c>
+      <c r="P30" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>0</v>
+      </c>
+      <c r="R30" s="1">
+        <v>0</v>
+      </c>
+      <c r="S30" s="1">
+        <v>0</v>
+      </c>
+      <c r="T30" s="1">
+        <v>1</v>
+      </c>
+      <c r="U30" s="1">
+        <v>1</v>
+      </c>
+      <c r="V30" s="1">
+        <v>0</v>
+      </c>
+      <c r="W30" s="1">
+        <v>0</v>
+      </c>
+      <c r="X30" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z30" s="1">
+        <f t="shared" si="18"/>
+        <v>5</v>
+      </c>
+      <c r="AA30" s="1">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AB30" s="1">
+        <f t="shared" si="20"/>
+        <v>2</v>
+      </c>
+      <c r="AC30" s="1">
+        <f t="shared" si="21"/>
+        <v>8</v>
+      </c>
+      <c r="AD30" s="1">
+        <f t="shared" si="22"/>
+        <v>4.166666666666667</v>
+      </c>
+      <c r="AE30" s="1">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="AF30" s="1">
+        <f t="shared" si="24"/>
+        <v>2</v>
+      </c>
+      <c r="AG30" s="1">
+        <f t="shared" si="25"/>
+        <v>2.3888888888888888</v>
+      </c>
     </row>
     <row r="31" spans="1:34">
-      <c r="C31" s="15"/>
+      <c r="A31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>0</v>
+      </c>
+      <c r="F31" s="15">
+        <v>2</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H31" s="27">
+        <v>46140</v>
+      </c>
+      <c r="I31" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="J31" s="1">
+        <v>1</v>
+      </c>
+      <c r="K31" s="1">
+        <v>1</v>
+      </c>
+      <c r="L31" s="1">
+        <v>1</v>
+      </c>
+      <c r="M31" s="1">
+        <v>1</v>
+      </c>
+      <c r="N31" s="1">
+        <v>1</v>
+      </c>
+      <c r="O31" s="1">
+        <v>1</v>
+      </c>
+      <c r="P31" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="1">
+        <v>1</v>
+      </c>
+      <c r="R31" s="1">
+        <v>1</v>
+      </c>
+      <c r="S31" s="1">
+        <v>0</v>
+      </c>
+      <c r="T31" s="1">
+        <v>1</v>
+      </c>
+      <c r="U31" s="1">
+        <v>1</v>
+      </c>
+      <c r="V31" s="1">
+        <v>1</v>
+      </c>
+      <c r="W31" s="1">
+        <v>0</v>
+      </c>
+      <c r="X31" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="22">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="1">
+        <f t="shared" si="18"/>
+        <v>6</v>
+      </c>
+      <c r="AA31" s="1">
+        <f t="shared" si="19"/>
+        <v>3</v>
+      </c>
+      <c r="AB31" s="1">
+        <f t="shared" si="20"/>
+        <v>2</v>
+      </c>
+      <c r="AC31" s="1">
+        <f t="shared" si="21"/>
+        <v>11</v>
+      </c>
+      <c r="AD31" s="1">
+        <f t="shared" si="22"/>
+        <v>5</v>
+      </c>
+      <c r="AE31" s="1">
+        <f t="shared" si="23"/>
+        <v>3</v>
+      </c>
+      <c r="AF31" s="1">
+        <f t="shared" si="24"/>
+        <v>2</v>
+      </c>
+      <c r="AG31" s="1">
+        <f t="shared" si="25"/>
+        <v>3.3333333333333335</v>
+      </c>
     </row>
     <row r="32" spans="1:34">
-      <c r="C32" s="15"/>
+      <c r="A32" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" s="15">
+        <v>0</v>
+      </c>
+      <c r="E32" s="15">
+        <v>0</v>
+      </c>
+      <c r="F32" s="15">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H32" s="27">
+        <v>46140</v>
+      </c>
+      <c r="I32" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="J32" s="1">
+        <v>1</v>
+      </c>
+      <c r="K32" s="1">
+        <v>0</v>
+      </c>
+      <c r="L32" s="1">
+        <v>0</v>
+      </c>
+      <c r="M32" s="1">
+        <v>0</v>
+      </c>
+      <c r="N32" s="1">
+        <v>0</v>
+      </c>
+      <c r="O32" s="1">
+        <v>0</v>
+      </c>
+      <c r="P32" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>1</v>
+      </c>
+      <c r="R32" s="1">
+        <v>0</v>
+      </c>
+      <c r="S32" s="1">
+        <v>0</v>
+      </c>
+      <c r="T32" s="1">
+        <v>0</v>
+      </c>
+      <c r="U32" s="1">
+        <v>0</v>
+      </c>
+      <c r="V32" s="1">
+        <v>1</v>
+      </c>
+      <c r="W32" s="1">
+        <v>0</v>
+      </c>
+      <c r="X32" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y32" s="22">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="1">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="AA32" s="1">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="AB32" s="1">
+        <f t="shared" si="20"/>
+        <v>2</v>
+      </c>
+      <c r="AC32" s="1">
+        <f t="shared" si="21"/>
+        <v>4</v>
+      </c>
+      <c r="AD32" s="1">
+        <f t="shared" si="22"/>
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="AE32" s="1">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="AF32" s="1">
+        <f t="shared" si="24"/>
+        <v>2</v>
+      </c>
+      <c r="AG32" s="1">
+        <f t="shared" si="25"/>
+        <v>1.2777777777777777</v>
+      </c>
     </row>
     <row r="33" spans="3:3">
       <c r="C33" s="15"/>
@@ -5212,7 +5884,7 @@
         <v>2.1111111111111112</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI1" s="23"/>
     </row>
@@ -5222,15 +5894,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0278717-252d-455f-9297-341259384352">
@@ -5241,7 +5904,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006F98E057C991C64EA8C44B2688F4F4E8" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="205ac32a36de600e2ab9bca4f1502e82">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0278717-252d-455f-9297-341259384352" xmlns:ns3="67fd2e6b-9b4b-488b-ae5d-884371a2c380" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="423e538afa53ae88b73bb7a22e6ab62a" ns2:_="" ns3:_="">
     <xsd:import namespace="b0278717-252d-455f-9297-341259384352"/>
@@ -5430,14 +6093,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E6D151-5FDE-4AAE-92E5-7A931745F48E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86E1DA6F-9828-4C90-B1DD-F6C5DDCFA33D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86E1DA6F-9828-4C90-B1DD-F6C5DDCFA33D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32CEAB00-EB88-42CB-8573-B14217434AB6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32CEAB00-EB88-42CB-8573-B14217434AB6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E6D151-5FDE-4AAE-92E5-7A931745F48E}"/>
 </file>